--- a/CODE/Results/Results_2025_07_30.xlsx
+++ b/CODE/Results/Results_2025_07_30.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cityuni-my.sharepoint.com/personal/constantino-carlos_reyes-aldasoro_city_ac_uk/Documents/Documents/GitHub/Cilia/CODE/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{39262E28-34E0-4FA7-99B0-4F1D581024A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7201DD-312C-47D3-B16B-F89F078F5B0C}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{39262E28-34E0-4FA7-99B0-4F1D581024A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E087EF91-5DF6-4C46-BDF7-A4EC57002C8E}"/>
   <bookViews>
-    <workbookView xWindow="1716" yWindow="1788" windowWidth="21324" windowHeight="10272" activeTab="1" xr2:uid="{14D1A8FB-309E-479C-A942-4CDA6B923642}"/>
+    <workbookView xWindow="8256" yWindow="660" windowWidth="14220" windowHeight="11580" activeTab="2" xr2:uid="{14D1A8FB-309E-479C-A942-4CDA6B923642}"/>
   </bookViews>
   <sheets>
     <sheet name="Pixels" sheetId="1" r:id="rId1"/>
     <sheet name="microns" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="39">
   <si>
     <t>'Cilia_Exp_002_2025_07_11_NS_NEG_01_OVER.tif'</t>
   </si>
@@ -149,6 +151,12 @@
   <si>
     <t>Lengths individual cilia</t>
   </si>
+  <si>
+    <t>'Cilia_Exp_006_2025_09_01_FIB_48_NS_P28_09.tif'</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
 </sst>
 </file>
 
@@ -209,6 +217,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10633,4 +10645,290 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BCA8F8-1B0A-4368-AD04-83D4B581822C}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>12.8291023525</v>
+      </c>
+      <c r="D1">
+        <v>4.4465284565324001</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>255.985344615</v>
+      </c>
+      <c r="D2">
+        <v>20.926989530372399</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>10.656316101255401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>229.98616709000001</v>
+      </c>
+      <c r="D3">
+        <v>21.203758226206698</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>10.8418106504368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>361.38856759750001</v>
+      </c>
+      <c r="D4">
+        <v>32.219149935289899</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>9.68526341257013</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>173.46992217499999</v>
+      </c>
+      <c r="D5">
+        <v>19.151012541483102</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>9.6138596567141299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>300.95113525250002</v>
+      </c>
+      <c r="D6">
+        <v>25.8317863352115</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>15.854582816172799</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>254.6640749375</v>
+      </c>
+      <c r="D7">
+        <v>22.0643297210258</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>139.28739697</v>
+      </c>
+      <c r="D8">
+        <v>22.3119176512343</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>285.26638553250001</v>
+      </c>
+      <c r="D9">
+        <v>27.169069318225802</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>5.7324567269804696</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>332.61898590999999</v>
+      </c>
+      <c r="D10">
+        <v>26.679170540818699</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>11.621790499218401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>107.4064383</v>
+      </c>
+      <c r="D11">
+        <v>12.40673991383</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>12.2235311937297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>284.03035906000002</v>
+      </c>
+      <c r="D12">
+        <v>24.031620952302799</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>